--- a/GameConfig/Datas/叙事物品配置表.xlsx
+++ b/GameConfig/Datas/叙事物品配置表.xlsx
@@ -413,8 +413,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="55" customWidth="1" min="5" max="5"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -483,68 +490,69 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>##</t>
+          <t>##group</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>唯一ID</t>
+          <t>c</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>物品名称</t>
+          <t>c</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>物品描述</t>
+          <t>c</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>图片资源</t>
+          <t>c</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>部件ID列表</t>
+          <t>c</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>##group</t>
+          <t>##</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>唯一ID</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>物品名称</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>物品描述</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>图片资源</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>部件ID列表</t>
         </is>
       </c>
     </row>
     <row r="5">
+      <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
           <t>GLASS</t>
@@ -557,7 +565,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>一副陪伴陈父多年的旧眼镜。点按镜架、镜腿与镜片，查看它留下的记忆。</t>
+          <t>这是一个眼镜</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -572,6 +580,7 @@
       </c>
     </row>
     <row r="6">
+      <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
           <t>CAMERA</t>
@@ -584,7 +593,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>一台银色便携相机，快门卡住，镜头内部起雾。点按相机上的部位，查看它留下的记忆。</t>
+          <t>这是一个相机</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -594,11 +603,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CAMERA_PART_01,CAMERA_PART_02</t>
+          <t>CAMERA_PART_01,CAMERA_PART_02,CAMERA_PART_03</t>
         </is>
       </c>
     </row>
     <row r="7">
+      <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
           <t>CLOCK</t>
@@ -611,7 +621,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>一只停摆的旧座钟。点按钟面，查看它留下的记忆。</t>
+          <t>这是一个钟表</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -621,11 +631,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CLOCK_PART_01</t>
+          <t>CLOCK_PART_01,CLOCK_PART_02,CLOCK_PART_03</t>
         </is>
       </c>
     </row>
     <row r="8">
+      <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
           <t>DOLL</t>
@@ -633,12 +644,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>小白布偶</t>
+          <t>布布</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>一只破损的猫形布偶，侧缝开线，腹部填充物结块。图片来自项目已有陈果房间美术。</t>
+          <t>一个脏兮兮的小猫玩偶，头顶有些开线，漏出了一些棉花。</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -648,88 +659,63 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>DOLL_SEAM,DOLL_NOTE</t>
+          <t>DOLL_PART_01,DOLL_PART_02,DOLL_PART_03,DOLL_PART_04</t>
         </is>
       </c>
     </row>
     <row r="9">
+      <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>RADIO_DAD</t>
+          <t>RADIO</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>旧收音机</t>
+          <t>收录机</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>外壳磨损，读取模块损坏，存储部分暂时完好。引用项目已有修理铺收音机素材。</t>
+          <t>一个旧收音机，磁带仓盖卡死，无法打开。</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>scene_shop_old_radio</t>
+          <t>placeholder</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>RADIO_READER,RADIO_STORAGE</t>
+          <t>RADIO_PART_01,RADIO_PART_02,RADIO_PART_03,RADIO_PART_04</t>
         </is>
       </c>
     </row>
     <row r="10">
+      <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>RADIO_ZHOU</t>
+          <t>TAPE</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>老周的收音机</t>
+          <t>磁带</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>与陈先生的收音机型号相同，里面保存着老周朋友的一段声音。</t>
+          <t>磁带上贴着2017年3月25日的时间条。</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>scene_zhou_radio</t>
+          <t>placeholder</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ZHOU_RADIO_READER,ZHOU_RADIO_RECORDING</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>RADIO_REPAIRED</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>修好的收音机</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>读取模块已经更换，收音机重新通电。存储部分仍保留着家人的录音。</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>scene_shop_new_radio</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>RECORDING_NAME,RECORDING_PAUSE</t>
+          <t>TAPE_PART_01,TAPE_PART_02</t>
         </is>
       </c>
     </row>

--- a/GameConfig/Datas/叙事物品配置表.xlsx
+++ b/GameConfig/Datas/叙事物品配置表.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -552,7 +552,6 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
           <t>GLASS</t>
@@ -580,7 +579,6 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
           <t>CAMERA</t>
@@ -608,7 +606,6 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
           <t>CLOCK</t>
@@ -636,7 +633,6 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
           <t>DOLL</t>
@@ -664,7 +660,6 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
           <t>RADIO</t>
@@ -692,7 +687,6 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
           <t>TAPE</t>
@@ -716,6 +710,50 @@
       <c r="F10" t="inlineStr">
         <is>
           <t>TAPE_PART_01,TAPE_PART_02</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>WH_CLOCK_WALL</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>机械挂钟</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>嘀嗒，嘀嗒，声音很小，但很精准，似乎并不是你要找的东西。</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>WH_CLOCK_ALARM</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>小闹钟</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>放在桌子上的小小时钟，似乎还内置了闹铃的功能，应该不是老周想要的东西。</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>placeholder</t>
         </is>
       </c>
     </row>

--- a/GameConfig/Datas/叙事物品配置表.xlsx
+++ b/GameConfig/Datas/叙事物品配置表.xlsx
@@ -655,7 +655,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>DOLL_PART_01,DOLL_PART_02,DOLL_PART_03,DOLL_PART_04</t>
+          <t>DOLL_PART_01,DOLL_PART_02,DOLL_PART_03</t>
         </is>
       </c>
     </row>

--- a/GameConfig/Datas/叙事物品配置表.xlsx
+++ b/GameConfig/Datas/叙事物品配置表.xlsx
@@ -677,7 +677,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>placeholder</t>
+          <t>narrative_radio</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
